--- a/pipeline/credit_rating/output/visrating_xhtn_20261027.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20261027.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -650,7 +650,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q31" s="1" t="n">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q35" s="1" t="n">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q36" s="1" t="n">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q38" s="1" t="n">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q43" s="1" t="n">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q44" s="1" t="n">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q45" s="1" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q51" s="1" t="n">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q53" s="1" t="n">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q54" s="1" t="n">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q55" s="1" t="n">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q56" s="1" t="n">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q57" s="1" t="n">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q58" s="1" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q59" s="1" t="n">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q60" s="1" t="n">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q61" s="1" t="n">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q62" s="1" t="n">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q63" s="1" t="n">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q64" s="1" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q65" s="1" t="n">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q66" s="1" t="n">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q67" s="1" t="n">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q68" s="1" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q69" s="1" t="n">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q70" s="1" t="n">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q71" s="1" t="n">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q72" s="1" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q73" s="1" t="n">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q74" s="1" t="n">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q75" s="1" t="n">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q76" s="1" t="n">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q77" s="1" t="n">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q78" s="1" t="n">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q79" s="1" t="n">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q80" s="1" t="n">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q81" s="1" t="n">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q82" s="1" t="n">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q83" s="1" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q84" s="1" t="n">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q85" s="1" t="n">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q86" s="1" t="n">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q87" s="1" t="n">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q88" s="1" t="n">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q89" s="1" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q90" s="1" t="n">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q91" s="1" t="n">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q92" s="1" t="n">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q93" s="1" t="n">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q94" s="1" t="n">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q95" s="1" t="n">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q96" s="1" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q97" s="1" t="n">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q98" s="1" t="n">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q99" s="1" t="n">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q100" s="1" t="n">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q101" s="1" t="n">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q102" s="1" t="n">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q103" s="1" t="n">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q104" s="1" t="n">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q105" s="1" t="n">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q106" s="1" t="n">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q107" s="1" t="n">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q108" s="1" t="n">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q109" s="1" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q110" s="1" t="n">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q111" s="1" t="n">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q112" s="1" t="n">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q113" s="1" t="n">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q114" s="1" t="n">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q115" s="1" t="n">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q116" s="1" t="n">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q117" s="1" t="n">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q118" s="1" t="n">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q119" s="1" t="n">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q120" s="1" t="n">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q121" s="1" t="n">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q122" s="1" t="n">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q123" s="1" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="Q124" s="1" t="n">

--- a/pipeline/credit_rating/output/visrating_xhtn_20261027.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20261027.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -650,7 +650,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q31" s="1" t="n">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q35" s="1" t="n">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q36" s="1" t="n">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q38" s="1" t="n">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q43" s="1" t="n">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q44" s="1" t="n">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q45" s="1" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q51" s="1" t="n">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q53" s="1" t="n">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q54" s="1" t="n">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q55" s="1" t="n">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q56" s="1" t="n">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q57" s="1" t="n">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q58" s="1" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q59" s="1" t="n">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q60" s="1" t="n">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q61" s="1" t="n">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q62" s="1" t="n">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q63" s="1" t="n">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q64" s="1" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q65" s="1" t="n">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q66" s="1" t="n">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q67" s="1" t="n">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q68" s="1" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q69" s="1" t="n">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q70" s="1" t="n">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q71" s="1" t="n">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q72" s="1" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q73" s="1" t="n">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q74" s="1" t="n">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q75" s="1" t="n">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q76" s="1" t="n">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q77" s="1" t="n">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q78" s="1" t="n">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q79" s="1" t="n">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q80" s="1" t="n">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q81" s="1" t="n">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q82" s="1" t="n">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q83" s="1" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q84" s="1" t="n">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q85" s="1" t="n">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q86" s="1" t="n">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q87" s="1" t="n">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q88" s="1" t="n">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q89" s="1" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q90" s="1" t="n">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q91" s="1" t="n">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q92" s="1" t="n">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q93" s="1" t="n">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q94" s="1" t="n">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q95" s="1" t="n">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q96" s="1" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q97" s="1" t="n">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q98" s="1" t="n">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q99" s="1" t="n">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q100" s="1" t="n">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q101" s="1" t="n">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q102" s="1" t="n">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q103" s="1" t="n">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q104" s="1" t="n">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q105" s="1" t="n">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q106" s="1" t="n">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q107" s="1" t="n">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q108" s="1" t="n">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q109" s="1" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q110" s="1" t="n">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q111" s="1" t="n">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q112" s="1" t="n">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q113" s="1" t="n">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q114" s="1" t="n">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q115" s="1" t="n">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q116" s="1" t="n">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q117" s="1" t="n">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q118" s="1" t="n">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q119" s="1" t="n">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q120" s="1" t="n">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q121" s="1" t="n">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q122" s="1" t="n">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q123" s="1" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:44</t>
+          <t>2026-10-27 09:18:18</t>
         </is>
       </c>
       <c r="Q124" s="1" t="n">

--- a/pipeline/credit_rating/output/visrating_xhtn_20261027.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20261027.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -650,7 +650,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q31" s="1" t="n">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q35" s="1" t="n">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q36" s="1" t="n">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q38" s="1" t="n">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q43" s="1" t="n">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q44" s="1" t="n">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q45" s="1" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q51" s="1" t="n">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q53" s="1" t="n">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q54" s="1" t="n">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q55" s="1" t="n">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q56" s="1" t="n">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q57" s="1" t="n">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q58" s="1" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q59" s="1" t="n">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q60" s="1" t="n">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q61" s="1" t="n">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q62" s="1" t="n">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q63" s="1" t="n">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q64" s="1" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q65" s="1" t="n">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q66" s="1" t="n">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q67" s="1" t="n">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q68" s="1" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q69" s="1" t="n">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q70" s="1" t="n">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q71" s="1" t="n">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q72" s="1" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q73" s="1" t="n">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q74" s="1" t="n">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q75" s="1" t="n">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q76" s="1" t="n">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q77" s="1" t="n">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q78" s="1" t="n">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q79" s="1" t="n">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q80" s="1" t="n">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q81" s="1" t="n">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q82" s="1" t="n">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q83" s="1" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q84" s="1" t="n">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q85" s="1" t="n">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q86" s="1" t="n">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q87" s="1" t="n">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q88" s="1" t="n">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q89" s="1" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q90" s="1" t="n">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q91" s="1" t="n">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q92" s="1" t="n">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q93" s="1" t="n">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q94" s="1" t="n">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q95" s="1" t="n">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q96" s="1" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q97" s="1" t="n">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q98" s="1" t="n">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q99" s="1" t="n">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q100" s="1" t="n">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q101" s="1" t="n">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q102" s="1" t="n">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q103" s="1" t="n">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q104" s="1" t="n">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q105" s="1" t="n">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q106" s="1" t="n">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q107" s="1" t="n">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q108" s="1" t="n">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q109" s="1" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q110" s="1" t="n">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q111" s="1" t="n">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q112" s="1" t="n">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q113" s="1" t="n">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q114" s="1" t="n">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q115" s="1" t="n">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q116" s="1" t="n">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q117" s="1" t="n">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q118" s="1" t="n">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q119" s="1" t="n">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q120" s="1" t="n">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q121" s="1" t="n">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q122" s="1" t="n">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q123" s="1" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:18</t>
+          <t>2026-10-27 14:50:58</t>
         </is>
       </c>
       <c r="Q124" s="1" t="n">
